--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
@@ -930,12 +930,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -952,12 +952,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1398,22 +1398,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1424,26 +1428,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,15 +1716,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1742,22 +1746,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,18 +1776,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,22 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,26 +1832,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1858,26 +1862,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2860,26 +2860,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -2890,26 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2920,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2950,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2980,22 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3036,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3066,22 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3092,18 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3118,22 +3122,18 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,14 +3282,10 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3304,12 +3300,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3326,12 +3322,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3348,10 +3344,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,26 +3532,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3562,26 +3558,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -3592,22 +3588,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3622,18 +3614,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3648,18 +3644,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3719,11 +3719,11 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3922,18 +3922,18 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4010,26 +4010,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4070,22 +4070,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4100,22 +4100,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4130,26 +4130,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4160,22 +4160,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4556,24 +4556,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="n">
         <v>3</v>
       </c>
@@ -4586,18 +4578,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -4608,26 +4608,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4638,26 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4668,22 +4668,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4694,22 +4698,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4720,26 +4728,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4750,16 +4750,20 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4772,18 +4776,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4794,20 +4806,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4820,12 +4828,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -4842,26 +4850,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4872,26 +4876,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4902,26 +4902,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4932,26 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4962,26 +4962,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4992,16 +4984,24 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5014,17 +5014,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5044,26 +5044,26 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5074,22 +5074,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5240,26 +5240,22 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -5270,26 +5266,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -5300,22 +5292,26 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -5326,22 +5322,26 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -5538,22 +5538,18 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>$79B</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
           <t>$159.9B</t>
         </is>
       </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208">
@@ -5564,12 +5560,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$159.9B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -5586,18 +5582,22 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>$159.9B</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -5714,18 +5714,18 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216">
@@ -5736,18 +5736,18 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -5780,12 +5780,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -5802,12 +5802,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,22 +6194,18 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6220,18 +6216,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6242,15 +6242,19 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>3</v>
@@ -6264,19 +6268,15 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>3</v>
@@ -6290,22 +6290,18 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -6316,18 +6312,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -6564,26 +6564,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6594,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6624,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -6654,22 +6650,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F253" t="n">
@@ -6684,22 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6870,18 +6870,22 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -6896,22 +6900,18 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2-Year Note Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>4.211%</t>
+          <t>4.140%</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>2-Year Note Auction</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>4.140%</t>
+          <t>4.211%</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7178,18 +7178,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7204,22 +7204,26 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
@@ -7260,26 +7264,22 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -7290,18 +7290,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7790,22 +7790,18 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298">
@@ -7816,12 +7812,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,22 +7834,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7864,12 +7860,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7886,18 +7882,22 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7930,22 +7930,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8324,18 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8350,22 +8354,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,22 +8516,18 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F326" t="n">
@@ -8546,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -8576,26 +8572,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -8606,12 +8602,20 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr"/>
+          <t>Employment Cost - Benefits QoQQ4</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
       <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F329" t="n">
         <v>2</v>
       </c>
@@ -8624,26 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8654,26 +8658,14 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8684,7 +8676,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -8692,7 +8684,11 @@
           <t>0.9%</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8710,22 +8706,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
@@ -8736,26 +8736,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,26 +9768,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F376" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="377">
@@ -9798,18 +9794,18 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -9850,18 +9846,18 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F379" t="n">
@@ -9876,22 +9872,26 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/06</t>
+          <t>15-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>6.89%</t>
+          <t>6.05%</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -10456,12 +10456,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/06</t>
+          <t>30-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>6.05%</t>
+          <t>6.89%</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -10536,18 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10562,22 +10566,26 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -10588,26 +10596,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -10618,22 +10626,22 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10648,22 +10656,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10678,22 +10682,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10708,26 +10712,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -10738,26 +10742,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10768,22 +10768,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10794,26 +10794,26 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10904,22 +10904,18 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -10934,26 +10930,26 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F423" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="424">
@@ -10964,22 +10960,26 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
@@ -10990,22 +10990,18 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11020,22 +11016,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11050,18 +11046,22 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr"/>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -11564,22 +11564,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
@@ -11590,22 +11590,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -11616,7 +11612,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
@@ -11627,7 +11623,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -11642,22 +11638,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -11668,18 +11664,22 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F456" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
@@ -11690,18 +11690,18 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F457" t="n">
@@ -11716,14 +11716,14 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr"/>
       <c r="F458" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="459">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="464">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,14 +11842,14 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,14 +11976,14 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -11998,22 +11998,18 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="474">
@@ -12024,22 +12020,22 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="475">
@@ -12050,22 +12046,18 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -12076,18 +12068,14 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12102,18 +12090,22 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="478">
@@ -12124,14 +12116,18 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -12146,18 +12142,22 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480">
@@ -12168,22 +12168,22 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -12194,14 +12194,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -12574,18 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12600,22 +12600,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F500" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="501">
@@ -12626,14 +12622,14 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -12648,18 +12644,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12674,18 +12670,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13078,7 +13078,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -13302,7 +13302,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13338,7 +13338,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13428,14 +13428,14 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr"/>
       <c r="F542" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="543">
@@ -13464,7 +13464,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
@@ -13482,14 +13482,14 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr"/>
       <c r="F545" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="546">
@@ -13640,22 +13640,18 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -13688,18 +13684,22 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="555">
@@ -13970,14 +13970,22 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr"/>
-      <c r="E569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F569" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="570">
@@ -13988,14 +13996,22 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
-      <c r="D570" t="inlineStr"/>
-      <c r="E570" t="inlineStr"/>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F570" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="571">
@@ -14006,12 +14022,16 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
       <c r="D571" t="inlineStr"/>
-      <c r="E571" t="inlineStr"/>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F571" t="n">
         <v>3</v>
       </c>
@@ -14024,22 +14044,18 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
+      <c r="D572" t="inlineStr"/>
       <c r="E572" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F572" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="573">
@@ -14050,7 +14066,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
@@ -14068,22 +14084,14 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E574" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D574" t="inlineStr"/>
+      <c r="E574" t="inlineStr"/>
       <c r="F574" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="575">
@@ -14094,7 +14102,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
@@ -14112,7 +14120,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -14746,7 +14754,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14764,14 +14772,14 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="611">
@@ -14782,7 +14790,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14800,14 +14808,14 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
       <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr"/>
       <c r="F612" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="613">
@@ -14854,7 +14862,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14872,7 +14880,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14890,7 +14898,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -14908,7 +14916,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14926,7 +14934,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15442,18 +15450,18 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F643" t="n">
@@ -15468,18 +15476,18 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F644" t="n">
@@ -15494,22 +15502,22 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F645" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="646">
@@ -15520,22 +15528,22 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F646" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="647">
@@ -15546,18 +15554,18 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F647" t="n">
@@ -15572,18 +15580,22 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
-      <c r="D648" t="inlineStr"/>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F648" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="649">
@@ -15594,22 +15606,18 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
-      <c r="D649" t="inlineStr">
-        <is>
-          <t>4.17M</t>
-        </is>
-      </c>
+      <c r="D649" t="inlineStr"/>
       <c r="E649" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="650">
@@ -15674,7 +15682,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -15692,7 +15700,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -15944,7 +15952,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -16056,7 +16064,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
@@ -16074,18 +16082,14 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
-      <c r="E675" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E675" t="inlineStr"/>
       <c r="F675" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="676">
@@ -16096,14 +16100,18 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr"/>
-      <c r="E676" t="inlineStr"/>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F676" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="677">
@@ -16186,7 +16194,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -16204,14 +16212,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
       <c r="F682" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="683">
@@ -16240,7 +16248,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -16258,14 +16266,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="686">
@@ -16384,7 +16392,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -16402,7 +16410,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
@@ -930,12 +930,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -952,12 +952,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1398,26 +1398,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1428,22 +1424,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,26 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -1716,26 +1712,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1746,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1776,15 +1772,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1802,22 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1832,22 +1832,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1862,18 +1862,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2860,22 +2860,18 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2890,22 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2976,18 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3002,26 +3006,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3036,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3066,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3092,26 +3092,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3282,10 +3282,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3300,12 +3304,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3322,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3344,14 +3348,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,18 +3532,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -3558,12 +3562,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3573,11 +3577,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3588,18 +3592,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3614,22 +3622,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3644,26 +3652,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -3674,22 +3682,18 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,26 +3708,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3922,18 +3922,18 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4010,22 +4010,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -4040,26 +4040,26 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4070,22 +4070,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4100,22 +4100,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4130,22 +4130,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4160,26 +4160,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4556,16 +4556,24 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F170" t="n">
         <v>3</v>
       </c>
@@ -4578,26 +4586,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4608,26 +4608,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4638,26 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4668,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4698,26 +4694,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4728,12 +4720,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -4750,20 +4742,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4776,26 +4764,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4806,16 +4786,20 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4828,18 +4812,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4850,22 +4842,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4876,22 +4872,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4902,26 +4902,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4932,26 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4962,18 +4962,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -4984,24 +4992,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5014,22 +5014,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5044,17 +5044,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5074,26 +5074,26 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -5240,22 +5240,26 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -5266,22 +5270,26 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -5292,26 +5300,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -5322,26 +5326,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>$159.9B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5560,18 +5560,22 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>$159.9B</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -5582,22 +5586,18 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$79B</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
           <t>$159.9B</t>
         </is>
       </c>
+      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5736,18 +5736,18 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
@@ -5758,18 +5758,18 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -5802,12 +5802,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,18 +6194,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6216,22 +6220,18 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -6242,19 +6242,15 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>3</v>
@@ -6268,12 +6264,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,18 +6286,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -6312,22 +6312,18 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -6338,12 +6334,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,12 +6356,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,15 +6378,19 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
         <v>3</v>
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
@@ -6564,22 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6590,22 +6594,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -6620,26 +6624,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6650,26 +6654,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6870,22 +6870,18 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -6900,18 +6896,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>2-Year Note Auction</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>4.140%</t>
+          <t>4.211%</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2-Year Note Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>4.211%</t>
+          <t>4.140%</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7178,18 +7178,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7204,26 +7204,22 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
@@ -7264,22 +7260,26 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
@@ -7290,18 +7290,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7790,12 +7790,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -7812,12 +7812,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7834,22 +7834,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7882,22 +7882,18 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -7908,12 +7904,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7930,22 +7926,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,12 +7952,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,18 +7974,22 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -8324,22 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8354,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -8524,7 +8524,11 @@
           <t>0.9%</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8542,26 +8546,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -8572,26 +8576,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -8602,22 +8606,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -8628,26 +8636,14 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -8658,12 +8654,20 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr"/>
+          <t>Employment Cost - Benefits QoQQ4</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F331" t="n">
         <v>2</v>
       </c>
@@ -8676,26 +8680,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8706,26 +8710,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8736,22 +8740,18 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,22 +9768,26 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F376" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
@@ -9794,18 +9798,18 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -9846,18 +9850,18 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F379" t="n">
@@ -9872,26 +9876,22 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="381">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/06</t>
+          <t>30-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>6.05%</t>
+          <t>6.89%</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -10456,12 +10456,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/06</t>
+          <t>15-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>6.89%</t>
+          <t>6.05%</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -10536,26 +10536,26 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -10566,26 +10566,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -10596,26 +10592,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -10626,22 +10622,22 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10656,22 +10652,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -10682,22 +10678,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10712,26 +10708,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -10742,22 +10738,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416">
@@ -10768,18 +10768,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10794,22 +10798,18 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F417" t="n">
@@ -10904,18 +10904,22 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -10930,22 +10934,18 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,26 +10960,26 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="425">
@@ -10990,22 +10990,26 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F425" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="426">
@@ -11016,22 +11020,18 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11046,22 +11046,22 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -11564,18 +11564,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -11590,18 +11590,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -11612,22 +11616,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -11638,22 +11642,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -11664,22 +11668,18 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F456" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="457">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F457" t="n">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="461">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,14 +11842,14 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="466">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,18 +11976,22 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473">
@@ -11998,14 +12002,14 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12020,22 +12024,22 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -12046,18 +12050,22 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -12068,14 +12076,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12090,22 +12102,18 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478">
@@ -12116,18 +12124,14 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -12142,22 +12146,22 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -12168,22 +12172,18 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -12194,14 +12194,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -12574,18 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12600,14 +12600,14 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12622,18 +12622,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12644,18 +12648,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12670,22 +12674,18 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13078,7 +13078,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13338,7 +13338,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
@@ -13640,18 +13640,22 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
@@ -13684,22 +13688,18 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="555">
@@ -14754,14 +14754,14 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="610">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14790,14 +14790,14 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="612">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14880,7 +14880,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14898,7 +14898,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14934,7 +14934,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15450,18 +15450,18 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F643" t="n">
@@ -15476,22 +15476,22 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F644" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="645">
@@ -15502,22 +15502,22 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F645" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="646">
@@ -15528,18 +15528,18 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F646" t="n">
@@ -15554,18 +15554,18 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F647" t="n">
@@ -15580,22 +15580,18 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
-      <c r="D648" t="inlineStr">
-        <is>
-          <t>4.17M</t>
-        </is>
-      </c>
+      <c r="D648" t="inlineStr"/>
       <c r="E648" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F648" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="649">
@@ -15606,18 +15602,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
-      <c r="D649" t="inlineStr"/>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="650">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -16064,14 +16064,18 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr"/>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F674" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="675">
@@ -16082,7 +16086,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -16100,18 +16104,14 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr"/>
-      <c r="E676" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E676" t="inlineStr"/>
       <c r="F676" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="677">
@@ -16194,14 +16194,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -16266,14 +16266,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -16410,7 +16410,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
@@ -930,12 +930,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -952,12 +952,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1398,22 +1398,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1424,26 +1428,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,26 +1686,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1716,18 +1716,18 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,26 +1772,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -1802,22 +1798,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1832,15 +1828,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1858,22 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2860,26 +2860,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -2890,26 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2920,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2950,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2980,22 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3036,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3066,22 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3092,18 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3118,22 +3122,18 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,14 +3282,10 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3304,12 +3300,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3326,12 +3322,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3348,10 +3344,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,26 +3532,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3562,26 +3558,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -3592,18 +3588,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,22 +3618,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3648,18 +3648,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3674,22 +3678,18 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3719,11 +3719,11 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3922,18 +3922,18 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4010,22 +4010,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4070,26 +4070,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4100,22 +4100,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4130,26 +4130,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -4160,22 +4160,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4556,24 +4556,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="n">
         <v>3</v>
       </c>
@@ -4586,18 +4578,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -4608,26 +4608,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4638,26 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4668,22 +4668,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4694,22 +4698,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4720,12 +4728,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -4742,16 +4750,20 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4764,26 +4776,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4794,20 +4798,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4820,18 +4820,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4842,26 +4850,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4872,26 +4876,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4902,26 +4902,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4932,26 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4962,26 +4962,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4992,16 +4984,24 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5014,22 +5014,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5044,17 +5044,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5074,26 +5074,26 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -5240,26 +5240,22 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -5270,26 +5266,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -5300,22 +5292,26 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -5326,22 +5322,26 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>$159.9B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5560,18 +5560,22 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>$159.9B</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -5582,22 +5586,18 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$79B</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
           <t>$159.9B</t>
         </is>
       </c>
+      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
@@ -5714,18 +5714,18 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216">
@@ -5736,12 +5736,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -5758,12 +5758,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -5780,12 +5780,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -5802,18 +5802,18 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,22 +6194,18 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6220,18 +6216,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6264,15 +6264,19 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>3</v>
@@ -6286,22 +6290,18 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -6312,18 +6312,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6334,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6356,19 +6360,15 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
         <v>3</v>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6534,22 +6534,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6564,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6594,26 +6594,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6624,22 +6624,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6650,26 +6654,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6684,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6714,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6870,18 +6870,22 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -6896,22 +6900,18 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2-Year Note Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>4.211%</t>
+          <t>4.140%</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>2-Year Note Auction</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>4.140%</t>
+          <t>4.211%</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7178,18 +7178,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7204,22 +7204,26 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
@@ -7260,26 +7264,22 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -7290,18 +7290,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7790,12 +7790,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -7812,12 +7812,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7834,22 +7834,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7882,22 +7882,18 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -7908,12 +7904,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7930,22 +7926,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7956,12 +7952,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,18 +7974,22 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -8324,18 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8350,22 +8354,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,22 +8516,18 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F326" t="n">
@@ -8546,12 +8542,20 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr"/>
+          <t>Employment Cost - Benefits QoQQ4</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
       <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F327" t="n">
         <v>2</v>
       </c>
@@ -8564,26 +8568,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -8594,26 +8598,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8624,26 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8654,26 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8684,7 +8688,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -8692,7 +8696,11 @@
           <t>0.9%</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8710,26 +8718,14 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr"/>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8740,26 +8736,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -8770,22 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,26 +9768,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F376" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="377">
@@ -9798,18 +9794,18 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -9850,18 +9846,18 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F379" t="n">
@@ -9876,22 +9872,26 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/06</t>
+          <t>15-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>6.89%</t>
+          <t>6.05%</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -10456,12 +10456,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/06</t>
+          <t>30-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>6.05%</t>
+          <t>6.89%</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -10536,18 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10562,22 +10566,26 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -10588,26 +10596,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -10618,22 +10626,22 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10648,22 +10656,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10678,22 +10682,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10708,26 +10712,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -10738,26 +10742,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10768,22 +10768,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10794,26 +10794,26 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10904,22 +10904,26 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -10930,22 +10934,18 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,22 +10960,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10990,18 +10990,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr"/>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11016,22 +11020,18 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11046,26 +11046,26 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -11564,22 +11564,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
@@ -11590,22 +11590,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -11616,7 +11612,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
@@ -11627,7 +11623,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -11642,22 +11638,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -11668,18 +11664,22 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F456" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
@@ -11690,18 +11690,18 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F457" t="n">
@@ -11716,14 +11716,14 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr"/>
       <c r="F458" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="459">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="464">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,14 +11860,14 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
       <c r="F466" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="467">
@@ -11976,22 +11976,18 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="473">
@@ -12002,22 +11998,22 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="474">
@@ -12028,14 +12024,14 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -12050,22 +12046,18 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -12076,18 +12068,14 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12102,18 +12090,22 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="478">
@@ -12124,14 +12116,18 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -12146,14 +12142,14 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12168,18 +12164,22 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481">
@@ -12190,22 +12190,22 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="482">
@@ -12574,18 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12600,14 +12600,14 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12622,18 +12622,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12644,18 +12648,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12670,22 +12674,18 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13078,7 +13078,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13338,7 +13338,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
@@ -13640,22 +13640,18 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -13688,18 +13684,22 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="555">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14772,14 +14772,14 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="611">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14808,14 +14808,14 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
       <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr"/>
       <c r="F612" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="613">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14880,7 +14880,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14898,7 +14898,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14934,7 +14934,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15450,18 +15450,18 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F643" t="n">
@@ -15476,18 +15476,18 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F644" t="n">
@@ -15502,18 +15502,18 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F645" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F646" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="647">
@@ -15554,22 +15554,22 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F647" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="648">
@@ -15580,18 +15580,22 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
-      <c r="D648" t="inlineStr"/>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F648" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="649">
@@ -15602,22 +15606,18 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
-      <c r="D649" t="inlineStr">
-        <is>
-          <t>4.17M</t>
-        </is>
-      </c>
+      <c r="D649" t="inlineStr"/>
       <c r="E649" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="650">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -16064,7 +16064,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
@@ -16082,18 +16082,14 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
-      <c r="E675" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E675" t="inlineStr"/>
       <c r="F675" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="676">
@@ -16104,14 +16100,18 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr"/>
-      <c r="E676" t="inlineStr"/>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F676" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="677">
@@ -16194,14 +16194,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -16266,14 +16266,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="686">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -16410,7 +16410,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
@@ -930,12 +930,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -952,12 +952,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1398,26 +1398,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1428,22 +1424,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,15 +1716,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1742,22 +1746,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,18 +1776,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,22 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,26 +1832,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1858,26 +1862,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2860,22 +2860,18 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2890,22 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2976,18 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3002,26 +3006,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3036,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3066,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3092,26 +3092,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3282,10 +3282,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3300,12 +3304,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3322,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3344,14 +3348,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,18 +3532,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -3558,12 +3562,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3573,11 +3577,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3588,22 +3592,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,22 +3622,18 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3648,26 +3648,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -3678,18 +3678,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,26 +3708,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3922,18 +3922,18 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4010,22 +4010,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4070,22 +4070,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4100,26 +4100,26 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -4130,22 +4130,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4160,26 +4160,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -4556,16 +4556,24 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F170" t="n">
         <v>3</v>
       </c>
@@ -4578,26 +4586,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4608,26 +4608,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4638,26 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4668,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4698,26 +4694,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4728,18 +4720,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4750,20 +4750,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4776,12 +4772,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -4798,16 +4794,20 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4820,26 +4820,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4850,22 +4842,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4876,22 +4872,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4902,26 +4902,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4932,26 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4962,18 +4962,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -4984,24 +4992,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5014,26 +5014,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5044,22 +5044,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5074,17 +5074,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
@@ -5240,22 +5240,26 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -5266,22 +5270,26 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -5292,26 +5300,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -5322,26 +5326,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
@@ -5538,18 +5538,22 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>$159.9B</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208">
@@ -5560,22 +5564,18 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$79B</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
           <t>$159.9B</t>
         </is>
       </c>
+      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$159.9B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -5714,18 +5714,18 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216">
@@ -5736,18 +5736,18 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -5780,12 +5780,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -5802,12 +5802,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,18 +6194,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6216,22 +6220,18 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -6242,15 +6242,19 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>3</v>
@@ -6264,19 +6268,15 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>3</v>
@@ -6290,18 +6290,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -6312,22 +6316,18 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6534,26 +6534,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -6564,26 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6594,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6624,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -6654,26 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6684,22 +6680,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6714,22 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6870,22 +6870,18 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -6900,18 +6896,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>2-Year Note Auction</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>4.140%</t>
+          <t>4.211%</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2-Year Note Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>4.211%</t>
+          <t>4.140%</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7178,18 +7178,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7204,26 +7204,22 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
@@ -7264,22 +7260,26 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
@@ -7290,18 +7290,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7790,18 +7790,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -7812,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7834,22 +7838,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7860,12 +7864,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7882,12 +7886,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7904,12 +7908,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7926,22 +7930,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7952,12 +7956,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7974,22 +7978,18 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -8324,22 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8354,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -8524,7 +8524,11 @@
           <t>0.9%</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8542,22 +8546,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -8568,26 +8576,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -8598,26 +8606,14 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr"/>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8628,26 +8624,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -8658,26 +8654,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8688,26 +8684,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8718,12 +8714,20 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr"/>
+          <t>Employment Cost - Benefits QoQQ4</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
       <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F333" t="n">
         <v>2</v>
       </c>
@@ -8736,22 +8740,18 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,22 +9768,26 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F376" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
@@ -9794,18 +9798,18 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -9846,18 +9850,18 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F379" t="n">
@@ -9872,26 +9876,22 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="381">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/06</t>
+          <t>30-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>6.05%</t>
+          <t>6.89%</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -10456,12 +10456,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/06</t>
+          <t>15-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>6.89%</t>
+          <t>6.05%</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -10536,26 +10536,26 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -10566,26 +10566,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -10596,26 +10592,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -10626,22 +10622,22 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10656,22 +10652,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -10682,22 +10678,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10712,26 +10708,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -10742,22 +10738,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416">
@@ -10768,18 +10768,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10794,22 +10798,18 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F417" t="n">
@@ -10904,26 +10904,26 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
@@ -10934,22 +10934,26 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F423" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="424">
@@ -10960,22 +10964,18 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10990,22 +10990,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11020,18 +11020,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr"/>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11046,22 +11050,18 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -11564,18 +11564,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -11590,18 +11590,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -11612,22 +11616,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -11638,22 +11642,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -11664,22 +11668,18 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F456" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="457">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F457" t="n">
@@ -11716,14 +11716,14 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr"/>
       <c r="F458" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="459">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="461">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,14 +11842,14 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,14 +11976,14 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -11998,22 +11998,22 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="474">
@@ -12024,18 +12024,22 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475">
@@ -12046,18 +12050,22 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -12068,14 +12076,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12090,22 +12102,18 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478">
@@ -12116,18 +12124,14 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -12142,14 +12146,14 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12164,22 +12168,22 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -12190,22 +12194,18 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="482">
@@ -12574,18 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12600,18 +12600,22 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F500" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
@@ -12622,22 +12626,18 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="502">
@@ -12648,18 +12648,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12674,14 +12674,14 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F503" t="n">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13078,7 +13078,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13338,7 +13338,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
@@ -13640,18 +13640,22 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
@@ -13684,22 +13688,18 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="555">
@@ -14754,14 +14754,14 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="610">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14790,14 +14790,14 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="612">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14880,7 +14880,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14898,7 +14898,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14934,7 +14934,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15450,18 +15450,18 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F643" t="n">
@@ -15476,18 +15476,18 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F644" t="n">
@@ -15502,22 +15502,22 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F645" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="646">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F646" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="647">
@@ -15554,18 +15554,18 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F647" t="n">
@@ -15580,22 +15580,18 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
-      <c r="D648" t="inlineStr">
-        <is>
-          <t>4.17M</t>
-        </is>
-      </c>
+      <c r="D648" t="inlineStr"/>
       <c r="E648" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F648" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="649">
@@ -15606,18 +15602,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
-      <c r="D649" t="inlineStr"/>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="650">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -16064,14 +16064,18 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr"/>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F674" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="675">
@@ -16082,7 +16086,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -16100,18 +16104,14 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr"/>
-      <c r="E676" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E676" t="inlineStr"/>
       <c r="F676" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="677">
@@ -16194,14 +16194,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -16266,14 +16266,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -16410,7 +16410,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F700"/>
+  <dimension ref="A1:F707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,12 +930,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -952,12 +952,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1398,26 +1398,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1428,22 +1424,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,18 +1686,18 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1712,22 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,26 +1772,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1832,26 +1832,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1862,15 +1858,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2860,18 +2860,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2886,22 +2890,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2920,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2950,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2972,22 +2980,18 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3002,26 +3006,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3036,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3066,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3092,22 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3282,10 +3282,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3300,12 +3304,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3322,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3344,14 +3348,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3547,11 +3547,11 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -3562,18 +3562,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,18 +3592,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3614,22 +3622,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3644,26 +3652,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3674,22 +3678,18 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,26 +3704,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3922,18 +3922,18 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4010,22 +4010,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -4040,26 +4040,26 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4070,22 +4070,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4100,22 +4100,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4130,22 +4130,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4160,26 +4160,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4556,16 +4556,24 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F170" t="n">
         <v>3</v>
       </c>
@@ -4578,26 +4586,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4608,26 +4608,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4638,26 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4668,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4698,26 +4694,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4728,18 +4720,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4750,20 +4750,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4776,12 +4772,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -4798,12 +4794,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -4820,22 +4816,22 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4850,22 +4846,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4876,22 +4876,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4902,7 +4906,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4912,16 +4916,16 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4932,26 +4936,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -4962,12 +4966,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -4984,22 +4988,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5044,26 +5044,26 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5074,22 +5074,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5352,18 +5352,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5378,22 +5382,18 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,26 +5408,26 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
@@ -5438,22 +5438,18 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>77.6%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5468,22 +5464,26 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -5648,12 +5648,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -6150,15 +6150,19 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
         <v>3</v>
@@ -6172,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,22 +6198,18 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6220,18 +6220,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6242,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6264,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6286,22 +6290,18 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -6312,18 +6312,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6334,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6356,19 +6360,15 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
         <v>3</v>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6740,12 +6740,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/24</t>
+          <t>Baker Hughes Total Rigs CountJAN/24</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>576</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/24</t>
+          <t>Baker Hughes Oil Rig CountJAN/24</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>472</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7040,22 +7040,18 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F268" t="n">
@@ -7070,26 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -7100,26 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7130,22 +7126,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -7316,22 +7316,26 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
@@ -7342,18 +7346,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7368,22 +7376,18 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7398,26 +7402,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -7616,18 +7616,18 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
@@ -7638,18 +7638,18 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292">
@@ -7660,12 +7660,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7790,18 +7790,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -7812,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7834,12 +7838,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7856,22 +7860,18 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301">
@@ -8070,22 +8070,26 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F309" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
@@ -8096,18 +8100,18 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8122,22 +8126,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8152,18 +8156,18 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8178,22 +8182,22 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8208,12 +8212,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8227,7 +8231,7 @@
         </is>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -8238,26 +8242,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -8268,18 +8268,18 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,26 +8294,26 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -8516,26 +8516,26 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F326" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="327">
@@ -8546,18 +8546,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8572,15 +8576,19 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8598,26 +8606,14 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr"/>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8628,26 +8624,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -8658,14 +8654,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr"/>
-      <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
+          <t>Core PCE Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8676,22 +8684,18 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8706,26 +8710,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8736,26 +8736,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8904,26 +8904,26 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
@@ -8934,22 +8934,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8960,22 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -8990,22 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9016,26 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9206,22 +9206,26 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -9232,22 +9236,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -9258,26 +9266,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9288,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9590,18 +9590,18 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -9616,14 +9616,26 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr"/>
-      <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -9634,22 +9646,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9664,22 +9672,14 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -9924,15 +9924,19 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
         <v>3</v>
@@ -9946,18 +9950,22 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
@@ -9968,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -10016,12 +10024,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10038,12 +10046,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10060,22 +10068,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10086,19 +10090,15 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10536,22 +10536,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10566,18 +10562,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10592,26 +10592,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -10622,26 +10618,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -10652,26 +10648,26 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -10682,26 +10678,26 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -10712,26 +10708,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -10742,22 +10738,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416">
@@ -10768,22 +10768,18 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10798,18 +10794,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F417" t="n">
@@ -10904,22 +10904,18 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -10934,22 +10930,22 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10964,26 +10960,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="425">
@@ -10994,18 +10986,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr"/>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11020,22 +11016,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11050,22 +11046,26 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>4.185%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.185%</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -11474,14 +11474,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,14 +11546,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="461">
@@ -11770,14 +11770,14 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="462">
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,14 +11976,18 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -11998,18 +12002,14 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12024,18 +12024,22 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -12046,18 +12050,22 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476">
@@ -12068,18 +12076,22 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="477">
@@ -12090,22 +12102,18 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478">
@@ -12116,22 +12124,18 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="479">
@@ -12142,22 +12146,22 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -12168,14 +12172,14 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -12190,18 +12194,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -12288,7 +12288,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/13</t>
+          <t>30-Year Mortgage RateFEB/13</t>
         </is>
       </c>
       <c r="C486" t="inlineStr"/>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/13</t>
+          <t>15-Year Mortgage RateFEB/13</t>
         </is>
       </c>
       <c r="C487" t="inlineStr"/>
@@ -12360,14 +12360,14 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F490" t="n">
@@ -12382,22 +12382,18 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F491" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="492">
@@ -12408,18 +12404,14 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F492" t="n">
@@ -12434,7 +12426,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
@@ -12460,22 +12452,18 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -12486,14 +12474,18 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F495" t="n">
@@ -12508,18 +12500,22 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F496" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="497">
@@ -12530,14 +12526,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F497" t="n">
@@ -12552,18 +12548,22 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F498" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -12896,8 +12896,16 @@
         </is>
       </c>
       <c r="C514" t="inlineStr"/>
-      <c r="D514" t="inlineStr"/>
-      <c r="E514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="F514" t="n">
         <v>2</v>
       </c>
@@ -13060,7 +13068,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
@@ -13078,7 +13086,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13096,7 +13104,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
@@ -13222,18 +13230,14 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr"/>
       <c r="F531" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="532">
@@ -13244,7 +13248,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
@@ -13262,14 +13266,18 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
@@ -13280,18 +13288,14 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
-      <c r="D534" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D534" t="inlineStr"/>
       <c r="E534" t="inlineStr"/>
       <c r="F534" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="535">
@@ -13302,14 +13306,18 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr"/>
       <c r="F535" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="536">
@@ -13320,7 +13328,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13338,14 +13346,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -13356,7 +13364,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13374,7 +13382,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13410,7 +13418,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
@@ -13428,14 +13436,14 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr"/>
       <c r="F542" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="543">
@@ -13446,14 +13454,14 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
       <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr"/>
       <c r="F543" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="544">
@@ -13464,7 +13472,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
@@ -13482,14 +13490,14 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr"/>
       <c r="F545" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="546">
@@ -13500,7 +13508,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
@@ -13588,22 +13596,18 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F550" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="551">
@@ -13614,18 +13618,22 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F551" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="552">
@@ -13636,22 +13644,18 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -13662,18 +13666,22 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F553" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554">
@@ -13684,18 +13692,18 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F554" t="n">
@@ -13970,7 +13978,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
@@ -13988,22 +13996,14 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
-      <c r="D570" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E570" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D570" t="inlineStr"/>
+      <c r="E570" t="inlineStr"/>
       <c r="F570" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="571">
@@ -14014,22 +14014,14 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
-      <c r="D571" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E571" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D571" t="inlineStr"/>
+      <c r="E571" t="inlineStr"/>
       <c r="F571" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="572">
@@ -14040,14 +14032,14 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
       <c r="D572" t="inlineStr"/>
       <c r="E572" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F572" t="n">
@@ -14062,14 +14054,14 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
       <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F573" t="n">
@@ -14084,14 +14076,22 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr"/>
-      <c r="E574" t="inlineStr"/>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F574" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="575">
@@ -14120,14 +14120,22 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr"/>
-      <c r="E576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F576" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="577">
@@ -14156,14 +14164,22 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr"/>
-      <c r="E578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F578" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="579">
@@ -14174,18 +14190,18 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F579" t="n">
@@ -14200,22 +14216,18 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
-      <c r="D580" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
+      <c r="D580" t="inlineStr"/>
       <c r="E580" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F580" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="581">
@@ -14226,14 +14238,14 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr"/>
       <c r="E581" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F581" t="n">
@@ -14248,16 +14260,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E582" t="inlineStr"/>
       <c r="F582" t="n">
         <v>3</v>
       </c>
@@ -14270,7 +14278,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
@@ -14288,7 +14296,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
@@ -14306,7 +14314,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
@@ -14324,7 +14332,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
@@ -14466,7 +14474,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
@@ -14484,7 +14492,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
@@ -14538,14 +14546,14 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr"/>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="598">
@@ -14556,14 +14564,14 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr"/>
       <c r="F598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -14574,7 +14582,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
@@ -14592,7 +14600,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
@@ -14610,14 +14618,14 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -14628,7 +14636,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
@@ -14646,7 +14654,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
@@ -14664,14 +14672,14 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr"/>
       <c r="F604" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="605">
@@ -14682,7 +14690,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
@@ -14700,7 +14708,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14718,14 +14726,14 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="608">
@@ -14736,7 +14744,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14754,7 +14762,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14790,14 +14798,14 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="612">
@@ -14808,14 +14816,14 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
       <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr"/>
       <c r="F612" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="613">
@@ -14826,7 +14834,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -14844,7 +14852,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
@@ -14862,7 +14870,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14880,7 +14888,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14898,14 +14906,14 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr"/>
       <c r="F617" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="618">
@@ -14916,7 +14924,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14934,7 +14942,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15132,11 +15140,15 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
-      <c r="D630" t="inlineStr"/>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E630" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15176,15 +15188,11 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
-      <c r="D632" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="D632" t="inlineStr"/>
       <c r="E632" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15202,14 +15210,14 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
       <c r="D633" t="inlineStr"/>
       <c r="E633" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -15224,14 +15232,18 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
-      <c r="D634" t="inlineStr"/>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F634" t="n">
@@ -15246,15 +15258,11 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
-      <c r="D635" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15272,18 +15280,18 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F636" t="n">
@@ -15298,22 +15306,22 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F637" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="638">
@@ -15372,22 +15380,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F640" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="641">
@@ -15398,18 +15406,18 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F641" t="n">
@@ -15424,18 +15432,18 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F642" t="n">
@@ -15476,22 +15484,22 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F644" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="645">
@@ -15502,18 +15510,18 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F645" t="n">
@@ -15528,22 +15536,18 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
-      <c r="D646" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D646" t="inlineStr"/>
       <c r="E646" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F646" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="647">
@@ -15554,18 +15558,22 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
-      <c r="D647" t="inlineStr"/>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F647" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="648">
@@ -15576,22 +15584,22 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F648" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="649">
@@ -15602,22 +15610,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="650">
@@ -15664,7 +15672,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15682,7 +15690,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -15952,7 +15960,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15970,18 +15978,14 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
       <c r="D669" t="inlineStr"/>
-      <c r="E669" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E669" t="inlineStr"/>
       <c r="F669" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="670">
@@ -15992,7 +15996,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -16010,7 +16014,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -16046,7 +16050,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -16064,14 +16068,18 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr"/>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F674" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="675">
@@ -16104,7 +16112,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -16122,7 +16130,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -16158,14 +16166,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="680">
@@ -16212,7 +16220,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -16230,7 +16238,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
@@ -16266,14 +16274,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -16284,7 +16292,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16302,7 +16310,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16356,7 +16364,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16374,7 +16382,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
@@ -16464,7 +16472,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16482,7 +16490,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16500,7 +16508,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16546,6 +16554,132 @@
         <v>3</v>
       </c>
     </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2025-02-26 07:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr"/>
+      <c r="D701" t="inlineStr"/>
+      <c r="E701" t="inlineStr"/>
+      <c r="F701" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2025-02-26 07:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>MBA Purchase IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr"/>
+      <c r="D702" t="inlineStr"/>
+      <c r="E702" t="inlineStr"/>
+      <c r="F702" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2025-02-26 07:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Building Permits FinalJAN</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr"/>
+      <c r="D703" t="inlineStr"/>
+      <c r="E703" t="inlineStr"/>
+      <c r="F703" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2025-02-26 07:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>MBA Mortgage Market IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr"/>
+      <c r="D704" t="inlineStr"/>
+      <c r="E704" t="inlineStr"/>
+      <c r="F704" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2025-02-26 07:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr"/>
+      <c r="D705" t="inlineStr"/>
+      <c r="E705" t="inlineStr"/>
+      <c r="F705" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2025-02-26 07:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr"/>
+      <c r="D706" t="inlineStr"/>
+      <c r="E706" t="inlineStr"/>
+      <c r="F706" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2025-02-26 07:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Building Permits MoM FinalJAN</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr"/>
+      <c r="D707" t="inlineStr"/>
+      <c r="E707" t="inlineStr"/>
+      <c r="F707" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F707"/>
+  <dimension ref="A1:F709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,12 +930,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -952,12 +952,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1398,22 +1398,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1424,26 +1428,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,15 +1686,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1712,26 +1716,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1772,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1832,18 +1832,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2860,26 +2860,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -2890,26 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2920,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2950,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2980,22 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3036,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3066,22 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3092,18 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3118,22 +3122,18 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,14 +3282,10 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3304,12 +3300,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3326,12 +3322,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3348,10 +3344,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,26 +3532,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3562,26 +3558,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -3592,22 +3588,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3622,22 +3618,18 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3652,18 +3644,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3678,18 +3674,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3719,11 +3719,11 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3922,18 +3922,18 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4010,26 +4010,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4070,26 +4070,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4100,22 +4100,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4130,22 +4130,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4160,22 +4160,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4556,22 +4556,18 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -4586,12 +4582,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -4608,26 +4604,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -4638,7 +4634,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4648,16 +4644,16 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4668,22 +4664,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4694,22 +4694,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4720,26 +4724,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4750,12 +4746,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4772,18 +4768,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4794,18 +4798,26 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -4816,26 +4828,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4846,26 +4850,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4876,26 +4876,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4906,7 +4902,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4916,16 +4912,16 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4936,26 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4966,12 +4962,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -4988,18 +4984,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5352,26 +5352,26 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
@@ -5382,18 +5382,18 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,22 +5408,18 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>77.6%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5438,18 +5434,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5464,26 +5464,26 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -5648,12 +5648,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -6150,19 +6150,15 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
         <v>3</v>
@@ -6176,12 +6172,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,12 +6194,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,17 +6216,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2.5M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -6246,12 +6242,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,12 +6264,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,12 +6286,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6312,17 +6308,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>2.5M</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -6338,12 +6334,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,15 +6356,19 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
         <v>3</v>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6448,22 +6448,18 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>50.1</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -6508,18 +6504,22 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
+          <t>50.1</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -6784,22 +6784,22 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F258" t="n">
@@ -6814,22 +6814,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -7040,22 +7040,26 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -7066,26 +7070,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -7096,22 +7100,18 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F270" t="n">
@@ -7126,26 +7126,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -7316,26 +7316,22 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
@@ -7346,22 +7342,18 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7376,22 +7368,26 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -7402,18 +7398,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -7616,12 +7616,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7660,12 +7660,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7790,22 +7790,18 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298">
@@ -7816,18 +7812,22 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7860,12 +7860,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7882,15 +7882,19 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>3</v>
@@ -7904,19 +7908,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7930,12 +7930,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7952,17 +7952,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -7978,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8070,26 +8070,22 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F309" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="310">
@@ -8100,22 +8096,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>207K</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8126,22 +8126,18 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8156,18 +8152,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8212,22 +8212,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8242,18 +8238,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8268,18 +8268,18 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,26 +8294,26 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
@@ -8516,26 +8516,26 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F326" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -8546,22 +8546,18 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8576,19 +8572,15 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8606,14 +8598,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr"/>
-      <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr"/>
+          <t>Core PCE Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8624,26 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8654,26 +8658,14 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8684,15 +8676,19 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8710,18 +8706,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8736,26 +8736,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335">
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -8904,26 +8904,26 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341">
@@ -8934,18 +8934,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8960,26 +8964,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -8990,22 +8990,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -9016,22 +9020,18 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -9206,26 +9206,22 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="354">
@@ -9236,26 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -9266,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -9590,18 +9590,18 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -9616,26 +9616,14 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -9646,18 +9634,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9672,14 +9660,26 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -9924,19 +9924,15 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
         <v>3</v>
@@ -9950,22 +9946,18 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="384">
@@ -9976,18 +9968,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -9998,22 +9994,18 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386">
@@ -10024,18 +10016,22 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -10046,15 +10042,19 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>3</v>
@@ -10068,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10196,22 +10196,22 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F394" t="n">
@@ -10226,22 +10226,26 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr"/>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -10252,26 +10256,22 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>219K</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
@@ -10282,22 +10282,22 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F397" t="n">
@@ -10536,22 +10536,26 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -10562,26 +10566,26 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -10592,18 +10596,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10618,26 +10626,22 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>143K</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>170K</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -10648,26 +10652,26 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -10678,26 +10682,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -10708,26 +10708,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -10738,26 +10738,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10768,18 +10768,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10794,22 +10798,18 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F417" t="n">
@@ -10904,22 +10904,26 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -10930,22 +10934,22 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,18 +10964,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10986,22 +10994,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11016,22 +11024,18 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11046,26 +11050,22 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.185%</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>4.185%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -11474,14 +11474,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,14 +11546,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -11770,14 +11770,14 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="462">
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,18 +11976,14 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -12002,14 +11998,14 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12024,22 +12020,22 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="475">
@@ -12050,22 +12046,18 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -12076,22 +12068,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="477">
@@ -12102,14 +12090,14 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12124,18 +12112,22 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -12146,22 +12138,22 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -12172,14 +12164,18 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -12194,18 +12190,22 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="482">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -12360,18 +12360,22 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F490" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="491">
@@ -12382,18 +12386,22 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -12404,18 +12412,18 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -12426,22 +12434,18 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -12452,18 +12456,22 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
-      <c r="D494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -12474,18 +12482,14 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F495" t="n">
@@ -12500,22 +12504,18 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F496" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497">
@@ -12526,14 +12526,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F497" t="n">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
@@ -13068,7 +13068,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
@@ -13158,14 +13158,14 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr"/>
       <c r="F527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="528">
@@ -13176,14 +13176,14 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
       <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr"/>
       <c r="F528" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="529">
@@ -13194,14 +13194,14 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr"/>
       <c r="F529" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="530">
@@ -13212,14 +13212,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="531">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
@@ -13266,18 +13266,14 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="534">
@@ -13288,14 +13284,18 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr"/>
       <c r="F534" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="535">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13436,14 +13436,14 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr"/>
       <c r="F542" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="543">
@@ -13472,14 +13472,14 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr"/>
       <c r="F544" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="545">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
@@ -13526,22 +13526,18 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
-      <c r="D547" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F547" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="548">
@@ -13552,18 +13548,22 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F548" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="549">
@@ -13618,22 +13618,18 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D551" t="inlineStr"/>
       <c r="E551" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F551" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="552">
@@ -13644,18 +13640,22 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
@@ -13666,18 +13666,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F553" t="n">
@@ -13978,14 +13978,22 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr"/>
-      <c r="E569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F569" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="570">
@@ -13996,7 +14004,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
@@ -14014,7 +14022,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
@@ -14032,16 +14040,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
       <c r="D572" t="inlineStr"/>
-      <c r="E572" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E572" t="inlineStr"/>
       <c r="F572" t="n">
         <v>3</v>
       </c>
@@ -14054,14 +14058,14 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
       <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F573" t="n">
@@ -14076,22 +14080,18 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F574" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="575">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
@@ -14120,22 +14120,14 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E576" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D576" t="inlineStr"/>
+      <c r="E576" t="inlineStr"/>
       <c r="F576" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="577">
@@ -14146,14 +14138,22 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr"/>
-      <c r="E577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F577" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="578">
@@ -14238,16 +14238,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr"/>
-      <c r="E581" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E581" t="inlineStr"/>
       <c r="F581" t="n">
         <v>3</v>
       </c>
@@ -14260,7 +14256,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
@@ -14278,7 +14274,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
@@ -14296,7 +14292,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
@@ -14332,12 +14328,16 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
       <c r="D586" t="inlineStr"/>
-      <c r="E586" t="inlineStr"/>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F586" t="n">
         <v>3</v>
       </c>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
@@ -14492,7 +14492,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
@@ -14528,7 +14528,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
@@ -14546,14 +14546,14 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr"/>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="598">
@@ -14564,14 +14564,14 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr"/>
       <c r="F598" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="599">
@@ -14600,14 +14600,14 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -14618,7 +14618,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
@@ -14636,7 +14636,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
@@ -14654,7 +14654,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
@@ -14672,14 +14672,14 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr"/>
       <c r="F604" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="605">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
@@ -14708,14 +14708,14 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr"/>
       <c r="F606" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="607">
@@ -14726,14 +14726,14 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="608">
@@ -14744,14 +14744,14 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="609">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14906,7 +14906,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -14924,7 +14924,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14942,14 +14942,14 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
       <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr"/>
       <c r="F619" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="620">
@@ -15140,15 +15140,11 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
-      <c r="D630" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="D630" t="inlineStr"/>
       <c r="E630" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15188,11 +15184,15 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
-      <c r="D632" t="inlineStr"/>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E632" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15280,22 +15280,22 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F636" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="637">
@@ -15306,22 +15306,22 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F637" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="638">
@@ -15332,22 +15332,22 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F638" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="639">
@@ -15358,18 +15358,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
-      <c r="D639" t="inlineStr"/>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F639" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="640">
@@ -15380,22 +15384,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
@@ -15406,22 +15410,22 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F641" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="642">
@@ -15432,22 +15436,18 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
-      <c r="D642" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D642" t="inlineStr"/>
       <c r="E642" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F642" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="643">
@@ -15458,22 +15458,22 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F643" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="644">
@@ -15484,18 +15484,18 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F644" t="n">
@@ -15510,22 +15510,18 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
-      <c r="D645" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+      <c r="D645" t="inlineStr"/>
       <c r="E645" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F645" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="646">
@@ -15536,18 +15532,22 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
-      <c r="D646" t="inlineStr"/>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F646" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="647">
@@ -15558,22 +15558,22 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F647" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="648">
@@ -15584,22 +15584,22 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F648" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="649">
@@ -15610,18 +15610,18 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F649" t="n">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -15816,7 +15816,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -15960,14 +15960,18 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
       <c r="D668" t="inlineStr"/>
-      <c r="E668" t="inlineStr"/>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F668" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="669">
@@ -15978,7 +15982,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
@@ -16014,14 +16018,18 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr"/>
-      <c r="E671" t="inlineStr"/>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F671" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="672">
@@ -16032,7 +16040,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
@@ -16050,7 +16058,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -16068,18 +16076,14 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E674" t="inlineStr"/>
       <c r="F674" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="675">
@@ -16090,18 +16094,14 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
-      <c r="E675" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E675" t="inlineStr"/>
       <c r="F675" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="676">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -16184,7 +16184,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16562,14 +16562,14 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
       <c r="D701" t="inlineStr"/>
       <c r="E701" t="inlineStr"/>
       <c r="F701" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="702">
@@ -16580,14 +16580,14 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
       <c r="D702" t="inlineStr"/>
       <c r="E702" t="inlineStr"/>
       <c r="F702" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="703">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -16670,7 +16670,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
@@ -16680,6 +16680,42 @@
         <v>3</v>
       </c>
     </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2025-02-26 07:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Building Permits MoM FinalJAN</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr"/>
+      <c r="D708" t="inlineStr"/>
+      <c r="E708" t="inlineStr"/>
+      <c r="F708" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2025-02-26 07:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Building Permits MoM FinalJAN</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr"/>
+      <c r="D709" t="inlineStr"/>
+      <c r="E709" t="inlineStr"/>
+      <c r="F709" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F743"/>
+  <dimension ref="A1:F747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,18 +720,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -742,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -764,22 +768,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -790,15 +790,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -812,12 +816,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,19 +838,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -860,18 +860,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -882,12 +886,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -904,22 +908,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -974,12 +974,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,22 +1716,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1746,18 +1746,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1776,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1832,22 +1832,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1862,18 +1862,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2098,18 +2098,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2124,26 +2128,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2154,14 +2158,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+          <t>Total Vehicle SalesDEC</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>16.3M</t>
+        </is>
+      </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2172,26 +2188,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -2202,26 +2214,14 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>1848K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2306,15 +2306,19 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
         <v>3</v>
@@ -2328,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2350,22 +2354,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2424,19 +2424,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
         <v>3</v>
@@ -2450,18 +2446,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2860,18 +2860,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2886,22 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2972,22 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3002,22 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3032,26 +3036,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3066,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3092,22 +3096,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3122,18 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -3304,10 +3304,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3322,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3344,14 +3348,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,22 +3532,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -3558,12 +3562,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3573,11 +3577,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3588,26 +3592,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -3618,18 +3622,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3644,22 +3652,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3674,22 +3682,18 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,26 +3708,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -4010,26 +4010,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4040,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4070,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4130,26 +4126,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4160,22 +4156,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4190,22 +4186,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4252,22 +4252,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -4278,18 +4278,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4300,12 +4304,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,12 +4326,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4344,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4366,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4388,22 +4392,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4414,22 +4414,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -4586,22 +4586,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4616,26 +4616,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4646,26 +4646,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4676,24 +4672,16 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
         <v>3</v>
       </c>
@@ -4706,18 +4694,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4732,18 +4720,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4754,12 +4750,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4776,16 +4772,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4798,26 +4802,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4828,18 +4824,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4854,22 +4850,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -4880,26 +4880,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4910,22 +4910,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -4940,26 +4940,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -4992,12 +4992,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -5014,17 +5014,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5044,22 +5044,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5074,26 +5074,26 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -5352,26 +5352,26 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
@@ -5382,18 +5382,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,18 +5412,18 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5434,22 +5438,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5464,26 +5468,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -5648,12 +5648,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,22 +5942,18 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -6002,18 +5998,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6150,18 +6150,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -6172,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,12 +6198,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6216,18 +6220,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6238,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6260,19 +6268,15 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>3</v>
@@ -6286,12 +6290,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6308,22 +6312,18 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -6334,15 +6334,19 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6356,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6378,22 +6382,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
@@ -6564,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -6594,22 +6594,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6620,26 +6624,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -6650,26 +6654,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F255" t="n">
@@ -7040,26 +7040,22 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F268" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269">
@@ -7070,26 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -7100,22 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -7126,26 +7126,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7316,18 +7316,18 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -7342,26 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -7372,26 +7368,26 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -7402,18 +7398,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7704,18 +7704,22 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>$-105.4B</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -7760,22 +7764,18 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>$-105.4B</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -8324,22 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8354,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,18 +8516,22 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F326" t="n">
@@ -8542,26 +8546,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -8572,20 +8576,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="n">
         <v>2</v>
       </c>
@@ -8598,26 +8594,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -8628,26 +8624,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -8658,26 +8654,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8688,22 +8684,18 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8718,26 +8710,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8748,12 +8740,20 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
+          <t>Employment Cost - Wages QoQQ4</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F334" t="n">
         <v>2</v>
       </c>
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8904,18 +8904,22 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -8930,26 +8934,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8960,22 +8964,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -8986,22 +8994,18 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9016,26 +9020,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -9206,18 +9206,18 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F353" t="n">
@@ -9232,26 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9262,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9288,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9590,18 +9590,18 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -9616,14 +9616,26 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr"/>
-      <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -9634,18 +9646,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9660,26 +9672,14 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,22 +9794,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -9846,26 +9850,22 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -9902,22 +9902,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -9928,15 +9924,19 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
         <v>3</v>
@@ -9950,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,22 +9972,18 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -9998,12 +9994,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10020,12 +10016,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10042,12 +10038,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,22 +10060,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10090,18 +10086,22 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -10196,22 +10196,22 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F394" t="n">
@@ -10226,26 +10226,26 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396">
@@ -10256,22 +10256,26 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr"/>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397">
@@ -10282,26 +10286,26 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -10312,26 +10316,22 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>219K</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="399">
@@ -10536,22 +10536,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10566,26 +10562,26 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -10596,26 +10592,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -10626,26 +10622,22 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -10656,18 +10648,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10682,26 +10678,26 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -10712,22 +10708,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -10738,18 +10738,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr"/>
+          <t>3K</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>-2K</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F415" t="n">
@@ -10764,22 +10768,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10794,26 +10798,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>111K</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>141K</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10904,22 +10904,18 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -10934,22 +10930,22 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10964,26 +10960,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="425">
@@ -10994,22 +10986,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11024,18 +11016,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr"/>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11050,22 +11046,26 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428">
@@ -11564,22 +11564,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -11616,18 +11616,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -11638,22 +11642,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F457" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -12574,14 +12574,14 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12596,22 +12596,22 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F500" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
@@ -12622,22 +12622,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E501" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F501" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="502">
@@ -12648,18 +12648,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12674,14 +12670,18 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F503" t="n">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13050,7 +13050,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
@@ -13158,14 +13158,14 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr"/>
       <c r="F527" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="528">
@@ -13176,14 +13176,14 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
       <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr"/>
       <c r="F528" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="529">
@@ -13194,14 +13194,14 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr"/>
       <c r="F529" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="530">
@@ -13212,14 +13212,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="531">
@@ -13230,18 +13230,14 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr"/>
       <c r="F531" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="532">
@@ -13252,7 +13248,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
@@ -13292,14 +13288,18 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr"/>
       <c r="F534" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="535">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13400,7 +13400,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13418,14 +13418,14 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr"/>
       <c r="F541" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="542">
@@ -13436,14 +13436,14 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr"/>
       <c r="F542" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="543">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
@@ -13552,18 +13552,22 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F548" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="549">
@@ -13574,14 +13578,14 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr"/>
       <c r="E549" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F549" t="n">
@@ -13596,22 +13600,18 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F550" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="551">
@@ -13622,22 +13622,18 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D551" t="inlineStr"/>
       <c r="E551" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F551" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="552">
@@ -13648,18 +13644,22 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
@@ -13670,18 +13670,22 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F553" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554">
@@ -13692,22 +13696,18 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="555">
@@ -13978,14 +13978,22 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr"/>
-      <c r="E569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F569" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="570">
@@ -13996,7 +14004,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
@@ -14014,22 +14022,14 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
-      <c r="D571" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E571" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D571" t="inlineStr"/>
+      <c r="E571" t="inlineStr"/>
       <c r="F571" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="572">
@@ -14040,22 +14040,14 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E572" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D572" t="inlineStr"/>
+      <c r="E572" t="inlineStr"/>
       <c r="F572" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="573">
@@ -14066,22 +14058,18 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
-      <c r="D573" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F573" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="574">
@@ -14092,22 +14080,18 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
+      <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F574" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="575">
@@ -14118,18 +14102,22 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
-      <c r="D575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F575" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="576">
@@ -14140,18 +14128,22 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F576" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="577">
@@ -14162,14 +14154,22 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr"/>
-      <c r="E577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F577" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="578">
@@ -14180,7 +14180,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
@@ -14216,12 +14216,16 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr"/>
-      <c r="E580" t="inlineStr"/>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F580" t="n">
         <v>3</v>
       </c>
@@ -14234,12 +14238,16 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr"/>
-      <c r="E581" t="inlineStr"/>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F581" t="n">
         <v>3</v>
       </c>
@@ -14252,16 +14260,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E582" t="inlineStr"/>
       <c r="F582" t="n">
         <v>3</v>
       </c>
@@ -14274,16 +14278,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
       <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E583" t="inlineStr"/>
       <c r="F583" t="n">
         <v>3</v>
       </c>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
@@ -14332,7 +14332,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
@@ -14600,7 +14600,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
@@ -14618,14 +14618,14 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -14690,14 +14690,14 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr"/>
       <c r="E605" t="inlineStr"/>
       <c r="F605" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="606">
@@ -14708,14 +14708,14 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr"/>
       <c r="F606" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="607">
@@ -14744,14 +14744,14 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="609">
@@ -14762,14 +14762,14 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="610">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14942,14 +14942,14 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
       <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr"/>
       <c r="F619" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="620">
@@ -15210,11 +15210,15 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15232,14 +15236,14 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F634" t="n">
@@ -15254,18 +15258,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
-      <c r="D635" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F635" t="n">
@@ -15280,22 +15280,18 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
-      <c r="D636" t="inlineStr">
-        <is>
-          <t>4.17M</t>
-        </is>
-      </c>
+      <c r="D636" t="inlineStr"/>
       <c r="E636" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F636" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="637">
@@ -15306,18 +15302,18 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F637" t="n">
@@ -15332,18 +15328,22 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
-      <c r="D638" t="inlineStr"/>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F638" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="639">
@@ -15354,22 +15354,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F639" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="640">
@@ -15380,22 +15380,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F640" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="641">
@@ -15406,22 +15406,22 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F641" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="642">
@@ -15432,18 +15432,18 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F642" t="n">
@@ -15458,22 +15458,22 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F643" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="644">
@@ -15484,22 +15484,22 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F644" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="645">
@@ -15510,22 +15510,18 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
-      <c r="D645" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D645" t="inlineStr"/>
       <c r="E645" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F645" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="646">
@@ -15536,22 +15532,22 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F646" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="647">
@@ -15562,18 +15558,18 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F647" t="n">
@@ -15588,18 +15584,22 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
-      <c r="D648" t="inlineStr"/>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F648" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="649">
@@ -15610,18 +15610,18 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F649" t="n">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -15816,7 +15816,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -15960,7 +15960,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15978,7 +15978,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
@@ -15996,7 +15996,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -16032,18 +16032,14 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
       <c r="D672" t="inlineStr"/>
-      <c r="E672" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E672" t="inlineStr"/>
       <c r="F672" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="673">
@@ -16054,14 +16050,18 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr"/>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F673" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="674">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
@@ -16090,7 +16090,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -16108,18 +16108,14 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr"/>
-      <c r="E676" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E676" t="inlineStr"/>
       <c r="F676" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="677">
@@ -16130,14 +16126,18 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
       <c r="D677" t="inlineStr"/>
-      <c r="E677" t="inlineStr"/>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F677" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="678">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
@@ -16184,7 +16184,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -16220,14 +16220,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
       <c r="F682" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="683">
@@ -16238,14 +16238,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16490,14 +16490,14 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
       <c r="D697" t="inlineStr"/>
       <c r="E697" t="inlineStr"/>
       <c r="F697" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="698">
@@ -16508,14 +16508,14 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr"/>
       <c r="E698" t="inlineStr"/>
       <c r="F698" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="699">
@@ -16526,7 +16526,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16580,7 +16580,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16598,14 +16598,14 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
       <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="704">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -16634,14 +16634,14 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
       <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr"/>
       <c r="F705" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="706">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -16760,7 +16760,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -16796,14 +16796,14 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr"/>
       <c r="E714" t="inlineStr"/>
       <c r="F714" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="715">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
@@ -16832,14 +16832,14 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr"/>
       <c r="F716" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="717">
@@ -16850,14 +16850,14 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr"/>
       <c r="E717" t="inlineStr"/>
       <c r="F717" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="718">
@@ -16868,14 +16868,14 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
       <c r="D718" t="inlineStr"/>
       <c r="E718" t="inlineStr"/>
       <c r="F718" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="719">
@@ -16886,7 +16886,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
@@ -16922,7 +16922,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
@@ -16994,7 +16994,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C725" t="inlineStr"/>
@@ -17012,14 +17012,14 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr"/>
       <c r="F726" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="727">
@@ -17030,14 +17030,14 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
       <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr"/>
       <c r="F727" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="728">
@@ -17048,14 +17048,14 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr"/>
       <c r="F728" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="729">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
@@ -17102,14 +17102,14 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr"/>
       <c r="E731" t="inlineStr"/>
       <c r="F731" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="732">
@@ -17192,7 +17192,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -17282,7 +17282,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
@@ -17328,6 +17328,78 @@
         <v>3</v>
       </c>
     </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2025-02-26 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>7-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr"/>
+      <c r="D744" t="inlineStr"/>
+      <c r="E744" t="inlineStr"/>
+      <c r="F744" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2025-02-26 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>2-Year FRN Auction</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr"/>
+      <c r="D745" t="inlineStr"/>
+      <c r="E745" t="inlineStr"/>
+      <c r="F745" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2025-02-26 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>7-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr"/>
+      <c r="D746" t="inlineStr"/>
+      <c r="E746" t="inlineStr"/>
+      <c r="F746" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2025-02-26 13:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Building Permits MoM FinalJAN</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr"/>
+      <c r="D747" t="inlineStr"/>
+      <c r="E747" t="inlineStr"/>
+      <c r="F747" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
@@ -720,22 +720,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -746,12 +742,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,18 +764,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -790,19 +790,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -816,18 +812,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -838,15 +838,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -860,22 +864,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -886,12 +886,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -974,12 +974,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,22 +1716,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1746,22 +1746,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1776,18 +1772,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,22 +1798,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1832,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1862,18 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2098,26 +2098,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>1848K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -2128,26 +2116,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2158,26 +2142,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2188,18 +2172,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2214,14 +2202,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+          <t>Total Vehicle SalesDEC</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>16.3M</t>
+        </is>
+      </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2306,19 +2306,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
         <v>3</v>
@@ -2332,12 +2328,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,12 +2350,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,18 +2372,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2446,22 +2446,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2472,12 +2468,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2494,15 +2490,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
         <v>3</v>
@@ -2860,22 +2860,18 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2890,22 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,22 +2972,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3006,22 +3002,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3036,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3066,26 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3096,22 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3122,18 +3118,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,14 +3282,10 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3304,12 +3300,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3326,12 +3322,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3348,10 +3344,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,26 +3532,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3562,26 +3562,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3592,22 +3588,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3622,22 +3614,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3652,12 +3644,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3667,11 +3659,11 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3682,22 +3674,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -3708,18 +3704,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -4010,22 +4010,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -4036,22 +4040,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4070,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4126,26 +4130,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -4156,22 +4160,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4186,26 +4190,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4252,22 +4252,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -4278,22 +4278,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4304,12 +4300,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4326,12 +4322,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4348,12 +4344,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,12 +4366,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,18 +4388,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4414,22 +4414,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -4586,22 +4586,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4616,26 +4616,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4646,22 +4646,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -4672,12 +4676,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -4694,18 +4698,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4720,26 +4724,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4750,16 +4746,24 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4772,24 +4776,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4802,18 +4798,26 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -4824,18 +4828,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4850,26 +4854,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4880,26 +4880,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4910,22 +4910,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -4940,26 +4940,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -4992,12 +4992,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -5014,22 +5014,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5044,26 +5044,26 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5074,17 +5074,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
@@ -5352,26 +5352,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201">
@@ -5382,22 +5378,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5412,18 +5408,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5438,26 +5438,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -5468,18 +5468,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -5648,12 +5648,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,18 +5942,22 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -5998,22 +6002,18 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6150,22 +6150,18 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
@@ -6176,12 +6172,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,15 +6194,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6220,22 +6220,18 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -6246,12 +6242,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,12 +6264,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,12 +6286,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6312,18 +6308,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6334,19 +6334,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6360,12 +6356,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,18 +6378,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -6534,22 +6534,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6564,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6594,26 +6594,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -6624,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6654,22 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7040,22 +7040,26 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -7066,26 +7070,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -7096,26 +7100,22 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7126,26 +7126,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -7316,18 +7316,22 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -7342,18 +7346,18 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7368,26 +7372,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
@@ -7398,26 +7398,26 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7704,22 +7704,18 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>$-105.4B</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -7764,18 +7760,22 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>$-105.4B</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -8324,18 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8350,22 +8354,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,22 +8516,18 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F326" t="n">
@@ -8546,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -8576,12 +8572,20 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr"/>
+          <t>Employment Cost - Wages QoQQ4</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F328" t="n">
         <v>2</v>
       </c>
@@ -8594,26 +8598,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8624,26 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8654,26 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
@@ -8684,20 +8688,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E332" t="inlineStr"/>
       <c r="F332" t="n">
         <v>2</v>
       </c>
@@ -8710,26 +8706,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8740,18 +8736,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -8904,22 +8904,18 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -8934,26 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
@@ -8964,26 +8956,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8994,18 +8986,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9020,22 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9206,22 +9206,26 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="354">
@@ -9232,26 +9236,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,18 +9262,18 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F355" t="n">
@@ -9288,26 +9288,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9590,18 +9590,18 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -9616,26 +9616,14 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -9646,18 +9634,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9672,14 +9660,26 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,26 +9794,22 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -9850,22 +9846,26 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -9902,18 +9902,22 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
@@ -9924,22 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9950,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9994,12 +9998,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10016,12 +10020,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10038,15 +10042,19 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>3</v>
@@ -10060,22 +10068,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10086,22 +10090,18 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390">
@@ -10196,26 +10196,22 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>219K</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
@@ -10226,26 +10222,26 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -10256,26 +10252,26 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
@@ -10286,22 +10282,22 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F397" t="n">
@@ -10316,22 +10312,26 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr"/>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399">
@@ -10536,22 +10536,26 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -10562,26 +10566,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>111K</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>141K</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -10592,22 +10592,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10622,18 +10622,22 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr"/>
+          <t>3K</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>-2K</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10648,26 +10652,26 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -10678,22 +10682,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10708,26 +10708,22 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -10738,26 +10734,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416">
@@ -10768,26 +10764,26 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10798,18 +10794,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F417" t="n">
@@ -10904,22 +10904,26 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -10930,22 +10934,22 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,18 +10964,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10986,22 +10994,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11016,22 +11024,18 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11046,26 +11050,22 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -11564,22 +11564,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -11616,22 +11616,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -11642,18 +11638,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F457" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="458">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -12574,14 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12596,22 +12600,22 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E500" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F500" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="501">
@@ -12622,18 +12626,14 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -12648,14 +12648,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12670,22 +12670,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
@@ -13158,14 +13158,14 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr"/>
       <c r="F527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="528">
@@ -13212,14 +13212,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="531">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
@@ -13578,18 +13578,22 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F549" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550">
@@ -13644,22 +13648,18 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -13670,22 +13670,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F553" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -13696,18 +13692,22 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="555">
@@ -14180,12 +14180,16 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr"/>
-      <c r="E578" t="inlineStr"/>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F578" t="n">
         <v>3</v>
       </c>
@@ -14198,12 +14202,16 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr"/>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F579" t="n">
         <v>3</v>
       </c>
@@ -14216,16 +14224,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr"/>
-      <c r="E580" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E580" t="inlineStr"/>
       <c r="F580" t="n">
         <v>3</v>
       </c>
@@ -14238,16 +14242,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr"/>
-      <c r="E581" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E581" t="inlineStr"/>
       <c r="F581" t="n">
         <v>3</v>
       </c>
@@ -14260,7 +14260,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
@@ -14278,7 +14278,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
@@ -14546,14 +14546,14 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr"/>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="598">
@@ -14582,7 +14582,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
@@ -14600,7 +14600,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
@@ -14618,7 +14618,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
@@ -14636,7 +14636,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
@@ -14654,7 +14654,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -14708,14 +14708,14 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr"/>
       <c r="F606" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="607">
@@ -14744,14 +14744,14 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="609">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14942,14 +14942,14 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
       <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr"/>
       <c r="F619" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="620">
@@ -15210,18 +15210,14 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="D633" t="inlineStr"/>
       <c r="E633" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -15236,11 +15232,15 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
-      <c r="D634" t="inlineStr"/>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E634" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15258,14 +15258,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F635" t="n">
@@ -15280,18 +15280,22 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
-      <c r="D636" t="inlineStr"/>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F636" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="637">
@@ -15302,18 +15306,18 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F637" t="n">
@@ -15328,22 +15332,22 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F638" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="639">
@@ -15354,22 +15358,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F639" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="640">
@@ -15380,22 +15384,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F640" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
@@ -15458,18 +15462,18 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F643" t="n">
@@ -15610,22 +15614,18 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
-      <c r="D649" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D649" t="inlineStr"/>
       <c r="E649" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="650">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -16032,7 +16032,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
@@ -16050,18 +16050,14 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E673" t="inlineStr"/>
       <c r="F673" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="674">
@@ -16072,14 +16068,18 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr"/>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F674" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="675">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16580,7 +16580,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -16832,14 +16832,14 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr"/>
       <c r="F716" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="717">
@@ -16850,14 +16850,14 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr"/>
       <c r="E717" t="inlineStr"/>
       <c r="F717" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="718">
@@ -16886,14 +16886,14 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr"/>
       <c r="E719" t="inlineStr"/>
       <c r="F719" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="720">
@@ -16904,14 +16904,14 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
       <c r="D720" t="inlineStr"/>
       <c r="E720" t="inlineStr"/>
       <c r="F720" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="721">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
@@ -720,12 +720,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -742,12 +742,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -764,22 +764,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -790,15 +786,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -812,22 +812,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -838,19 +834,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -864,18 +856,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -886,12 +882,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -908,18 +904,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -974,12 +974,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,22 +1716,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1746,18 +1746,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,18 +1772,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,22 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,22 +1832,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,22 +1862,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2098,14 +2098,26 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+          <t>Total Vehicle SalesDEC</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>16.3M</t>
+        </is>
+      </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -2116,18 +2128,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2142,26 +2158,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2172,26 +2184,14 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>1848K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2202,26 +2202,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2328,15 +2328,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
         <v>3</v>
@@ -2350,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2372,22 +2376,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2424,18 +2424,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2446,12 +2450,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2468,12 +2472,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2490,19 +2494,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
         <v>3</v>
@@ -2860,18 +2860,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2886,22 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2972,22 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3002,22 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3032,26 +3036,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3066,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3092,22 +3096,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3122,18 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,10 +3282,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3300,12 +3304,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3322,14 +3326,10 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3532,22 +3532,18 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -3562,18 +3558,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,22 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -3614,12 +3618,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3629,11 +3633,11 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -3644,26 +3648,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3674,26 +3674,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -3704,22 +3704,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -4010,26 +4010,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4040,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4070,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4130,26 +4126,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4160,22 +4156,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4190,22 +4186,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4252,22 +4252,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -4278,18 +4278,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4300,12 +4304,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,12 +4326,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4344,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4366,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4388,22 +4392,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4414,22 +4414,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -4586,22 +4586,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4616,26 +4616,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4646,26 +4646,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4676,12 +4672,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -4698,18 +4694,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4724,18 +4720,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4746,24 +4750,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4776,12 +4772,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -4798,26 +4794,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4828,18 +4816,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4854,22 +4842,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -4880,26 +4872,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4910,22 +4902,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -4940,26 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4970,12 +4962,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -4992,16 +4984,24 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5014,26 +5014,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5044,17 +5044,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5074,22 +5074,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5352,18 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5378,26 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -5408,22 +5408,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5438,26 +5438,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -5468,18 +5464,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -5648,12 +5648,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,22 +5942,18 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -6002,18 +5998,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6150,18 +6150,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -6172,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,19 +6198,15 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6220,18 +6220,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6242,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6264,15 +6268,19 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>3</v>
@@ -6286,12 +6294,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6308,22 +6316,18 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -6334,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6356,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6378,22 +6382,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -6564,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -6594,22 +6594,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6620,22 +6624,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6650,26 +6654,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -7040,26 +7040,22 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F268" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269">
@@ -7070,26 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -7100,22 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -7126,26 +7126,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7316,26 +7316,26 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
@@ -7346,18 +7346,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7372,18 +7376,18 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7398,26 +7402,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7704,18 +7704,22 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>$-105.4B</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -7760,22 +7764,18 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>$-105.4B</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -8324,22 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8354,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,20 +8516,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E326" t="inlineStr"/>
       <c r="F326" t="n">
         <v>2</v>
       </c>
@@ -8542,26 +8534,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -8572,18 +8564,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8598,26 +8594,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8628,26 +8624,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -8658,26 +8654,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8688,12 +8684,20 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
+          <t>Employment Cost - Wages QoQQ4</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F332" t="n">
         <v>2</v>
       </c>
@@ -8706,26 +8710,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8736,22 +8740,18 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8904,18 +8904,22 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -8930,22 +8934,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -8956,26 +8964,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -8986,22 +8990,18 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9016,26 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9206,26 +9206,26 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -9236,18 +9236,18 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
@@ -9262,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -9288,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9590,18 +9590,18 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -9616,14 +9616,26 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr"/>
-      <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -9634,18 +9646,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9660,26 +9672,14 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,22 +9794,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -9846,26 +9850,22 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -9902,22 +9902,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -9928,22 +9924,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9954,12 +9946,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9976,12 +9968,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9998,15 +9990,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10020,12 +10016,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10042,22 +10038,22 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -10068,18 +10064,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10196,22 +10196,26 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr"/>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395">
@@ -10222,22 +10226,22 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F395" t="n">
@@ -10252,26 +10256,26 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397">
@@ -10282,26 +10286,22 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>219K</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="398">
@@ -10312,26 +10312,26 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="399">
@@ -10536,26 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="409">
@@ -10566,18 +10562,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10592,26 +10592,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -10622,26 +10622,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -10652,22 +10652,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10682,22 +10678,26 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -10708,18 +10708,22 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr"/>
+          <t>3K</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>-2K</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F414" t="n">
@@ -10734,22 +10738,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F415" t="n">
@@ -10764,26 +10768,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>111K</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>141K</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -10794,26 +10794,26 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -10904,26 +10904,22 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
@@ -10934,22 +10930,22 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10964,22 +10960,18 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10994,22 +10986,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11024,22 +11016,26 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F426" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427">
@@ -11050,18 +11046,22 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr"/>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -11564,22 +11564,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -11616,18 +11616,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -11638,22 +11642,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F457" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -12574,22 +12574,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -12600,18 +12600,14 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12626,14 +12622,14 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -12648,14 +12644,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12670,22 +12670,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E503" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
@@ -13158,14 +13158,14 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr"/>
       <c r="F527" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="528">
@@ -13212,14 +13212,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="531">
@@ -13230,14 +13230,18 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr"/>
       <c r="F531" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="532">
@@ -13266,18 +13270,14 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="534">
@@ -13578,22 +13578,18 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
-      <c r="D549" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D549" t="inlineStr"/>
       <c r="E549" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F549" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="550">
@@ -13648,18 +13644,22 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
@@ -13670,18 +13670,22 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F553" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554">
@@ -13692,22 +13696,18 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="555">
@@ -14546,14 +14546,14 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr"/>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="598">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -14708,14 +14708,14 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr"/>
       <c r="F606" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="607">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14924,7 +14924,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15210,14 +15210,14 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
       <c r="D633" t="inlineStr"/>
       <c r="E633" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -15232,18 +15232,14 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
-      <c r="D634" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F634" t="n">
@@ -15258,11 +15254,15 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
-      <c r="D635" t="inlineStr"/>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E635" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15358,22 +15358,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F639" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="640">
@@ -15462,22 +15462,18 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
-      <c r="D643" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F643" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="644">
@@ -15614,18 +15610,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
-      <c r="D649" t="inlineStr"/>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="650">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16580,7 +16580,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
@@ -720,18 +720,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -742,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -764,18 +768,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -786,19 +794,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -812,12 +816,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,15 +838,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -856,22 +864,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -882,12 +886,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -904,22 +908,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -974,12 +974,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,22 +1716,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1746,18 +1746,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1776,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1832,22 +1832,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1862,18 +1862,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2098,26 +2098,26 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -2128,26 +2128,14 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>1848K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2158,18 +2146,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2184,14 +2176,26 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+          <t>Total Vehicle SalesDEC</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>16.3M</t>
+        </is>
+      </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -2202,26 +2206,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2306,18 +2306,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -2328,19 +2332,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
         <v>3</v>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,12 +2376,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2424,22 +2424,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2450,12 +2446,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2472,15 +2468,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
         <v>3</v>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2860,22 +2860,18 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2890,22 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,22 +2972,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3006,22 +3002,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3036,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3066,26 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3096,22 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3122,18 +3118,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -3304,14 +3304,10 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3326,10 +3322,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3532,22 +3532,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -3558,22 +3562,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,26 +3592,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -3618,26 +3622,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3648,18 +3648,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3674,22 +3678,18 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3719,11 +3719,11 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -4010,22 +4010,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -4036,22 +4040,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4070,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4126,26 +4130,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -4156,22 +4160,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4186,26 +4190,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4252,22 +4252,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -4278,22 +4278,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4304,12 +4300,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4326,12 +4322,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4348,12 +4344,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,12 +4366,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,18 +4388,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4414,22 +4414,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -4586,22 +4586,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4616,26 +4616,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4646,22 +4646,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -4672,12 +4676,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -4694,18 +4698,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4720,26 +4724,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4750,12 +4746,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4772,12 +4768,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -4794,18 +4790,26 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -4816,18 +4820,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4842,26 +4846,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4872,26 +4872,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4902,22 +4902,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -4932,26 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4962,16 +4962,24 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F185" t="n">
         <v>3</v>
       </c>
@@ -4984,24 +4992,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5014,17 +5014,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5044,22 +5044,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5074,26 +5074,26 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -5352,18 +5352,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5378,26 +5382,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -5408,26 +5408,26 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -5438,18 +5438,18 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -5648,12 +5648,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,18 +5942,22 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -5998,22 +6002,18 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6150,22 +6150,18 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
@@ -6176,12 +6172,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,12 +6194,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,22 +6216,18 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -6246,12 +6238,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,19 +6260,15 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>3</v>
@@ -6294,12 +6282,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6316,18 +6304,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6338,15 +6330,19 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6360,12 +6356,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,18 +6378,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
@@ -6564,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6594,26 +6594,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -6624,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -6654,22 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F255" t="n">
@@ -7040,22 +7040,26 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -7066,26 +7070,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -7096,26 +7100,22 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7126,26 +7126,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -7316,26 +7316,22 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
@@ -7346,26 +7342,26 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
@@ -7376,18 +7372,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7402,18 +7402,18 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7704,22 +7704,18 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>$-105.4B</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -7764,18 +7760,22 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>$-105.4B</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -8324,18 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8350,22 +8354,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,12 +8516,20 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr"/>
+          <t>Employment Cost - Wages QoQQ4</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F326" t="n">
         <v>2</v>
       </c>
@@ -8534,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -8564,22 +8572,18 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8594,26 +8598,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8624,26 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8654,26 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8684,18 +8688,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8710,26 +8718,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8740,20 +8748,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="n">
         <v>2</v>
       </c>
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -8904,22 +8904,18 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -8934,26 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8964,22 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -8990,18 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9016,26 +9020,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -9206,26 +9206,22 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="354">
@@ -9236,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -9292,18 +9292,18 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F356" t="n">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9590,18 +9590,18 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -9616,26 +9616,14 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -9646,18 +9634,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9672,14 +9660,26 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,26 +9794,22 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -9850,22 +9846,26 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -9924,18 +9924,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9946,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9968,15 +9972,19 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
         <v>3</v>
@@ -9990,22 +9998,22 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
@@ -10016,12 +10024,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10038,22 +10046,18 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
@@ -10064,22 +10068,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10196,26 +10196,26 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
@@ -10226,26 +10226,22 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>219K</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396">
@@ -10256,22 +10252,22 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -10286,22 +10282,26 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr"/>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -10312,26 +10312,26 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399">
@@ -10536,18 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
+          <t>3K</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>-2K</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10562,26 +10566,26 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -10592,26 +10596,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>111K</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>141K</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -10622,22 +10622,22 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10652,22 +10652,26 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -10678,26 +10682,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -10708,26 +10708,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -10738,26 +10738,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10768,18 +10768,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10794,22 +10798,18 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F417" t="n">
@@ -10904,18 +10904,22 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -10930,22 +10934,22 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,22 +10964,26 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
@@ -10986,22 +10994,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11016,26 +11024,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F426" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="427">
@@ -11046,22 +11050,18 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -11564,22 +11564,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -11616,22 +11616,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -11642,18 +11638,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F457" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="458">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -12574,22 +12574,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E499" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
@@ -12600,14 +12600,14 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12622,14 +12622,18 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -12644,22 +12648,22 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F502" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -12670,18 +12674,14 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F503" t="n">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
@@ -13158,14 +13158,14 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr"/>
       <c r="F527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="528">
@@ -13212,14 +13212,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="531">
@@ -13578,18 +13578,22 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F549" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550">
@@ -13644,22 +13648,18 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -13670,22 +13670,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F553" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -13696,18 +13692,22 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="555">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14924,7 +14924,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15210,11 +15210,15 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15232,14 +15236,14 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F634" t="n">
@@ -15254,18 +15258,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
-      <c r="D635" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F635" t="n">
@@ -15358,18 +15358,18 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F639" t="n">
@@ -15384,18 +15384,18 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F640" t="n">
@@ -15462,18 +15462,22 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
-      <c r="D643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F643" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="644">
@@ -15610,22 +15614,18 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
-      <c r="D649" t="inlineStr">
-        <is>
-          <t>4.17M</t>
-        </is>
-      </c>
+      <c r="D649" t="inlineStr"/>
       <c r="E649" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="650">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16580,7 +16580,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
@@ -720,22 +720,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -746,12 +742,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,22 +764,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -794,15 +786,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -816,18 +812,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -838,19 +838,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -864,18 +860,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -886,12 +886,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -974,12 +974,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,22 +1716,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1746,22 +1746,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1776,18 +1772,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,22 +1798,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1832,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1862,18 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2098,26 +2098,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -2128,14 +2124,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+          <t>Total Vehicle SalesDEC</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>16.3M</t>
+        </is>
+      </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2146,26 +2154,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>1848K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2176,26 +2172,26 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2206,18 +2202,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2306,22 +2306,18 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -2332,12 +2328,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,15 +2350,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
         <v>3</v>
@@ -2376,12 +2376,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2424,12 +2424,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2468,19 +2468,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
         <v>3</v>
@@ -2494,18 +2490,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2860,18 +2860,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2886,22 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2972,22 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3002,22 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3032,26 +3036,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3066,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3092,22 +3096,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3122,18 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -3304,10 +3304,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3322,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3344,14 +3348,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,26 +3532,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3577,11 +3577,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3592,22 +3592,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3622,18 +3618,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3678,22 +3678,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -3704,26 +3708,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -4010,26 +4010,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4040,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4070,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4130,26 +4126,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4160,22 +4156,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4190,22 +4186,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4252,22 +4252,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -4278,18 +4278,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4300,12 +4304,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,12 +4326,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4344,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4366,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4388,22 +4392,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4414,22 +4414,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -4586,22 +4586,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4616,26 +4616,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4646,26 +4646,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4676,16 +4672,24 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F174" t="n">
         <v>3</v>
       </c>
@@ -4698,18 +4702,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4724,18 +4728,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4746,12 +4758,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4768,12 +4780,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -4790,26 +4802,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4820,18 +4824,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4846,22 +4850,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -4872,26 +4880,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4902,22 +4910,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -4932,26 +4940,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4962,24 +4970,16 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
         <v>3</v>
       </c>
@@ -4992,12 +4992,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -5014,22 +5014,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5044,26 +5044,26 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5074,17 +5074,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
@@ -5352,22 +5352,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5382,18 +5382,18 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,26 +5408,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
@@ -5438,18 +5434,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5464,26 +5464,26 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -5648,12 +5648,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,22 +5942,18 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -6002,18 +5998,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6150,18 +6150,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -6172,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,15 +6198,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6216,18 +6224,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6238,12 +6250,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6260,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6282,12 +6294,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6304,22 +6316,18 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -6330,19 +6338,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6356,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6378,22 +6382,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6534,22 +6534,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6564,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -6594,22 +6594,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6620,26 +6624,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6650,26 +6654,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7040,26 +7040,22 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F268" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269">
@@ -7070,26 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -7100,22 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -7126,26 +7126,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7316,18 +7316,18 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -7342,26 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -7372,26 +7368,26 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -7402,18 +7398,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7704,18 +7704,22 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>$-105.4B</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -7760,22 +7764,18 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>$-105.4B</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -8324,22 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8354,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,18 +8516,22 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F326" t="n">
@@ -8542,26 +8546,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -8572,20 +8576,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="n">
         <v>2</v>
       </c>
@@ -8598,26 +8594,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8628,26 +8624,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -8658,26 +8654,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8688,22 +8684,18 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8718,26 +8710,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8748,12 +8740,20 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
+          <t>Employment Cost - Wages QoQQ4</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F334" t="n">
         <v>2</v>
       </c>
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8904,18 +8904,22 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -8930,26 +8934,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
@@ -8960,26 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8990,22 +8990,18 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9020,22 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9206,18 +9206,18 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F353" t="n">
@@ -9232,26 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9262,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9288,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9590,18 +9590,18 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -9616,14 +9616,26 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr"/>
-      <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -9634,18 +9646,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9660,26 +9672,14 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,22 +9794,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -9846,26 +9850,22 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -9924,22 +9924,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9950,12 +9946,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,22 +9968,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -9998,22 +9994,18 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386">
@@ -10024,12 +10016,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10046,18 +10038,22 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -10068,12 +10064,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10090,15 +10086,19 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10196,26 +10196,26 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395">
@@ -10226,22 +10226,26 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr"/>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -10252,26 +10256,22 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>219K</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
@@ -10282,26 +10282,26 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="398">
@@ -10312,22 +10312,22 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F398" t="n">
@@ -10536,26 +10536,26 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -10566,22 +10566,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10596,18 +10592,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10622,26 +10622,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -10652,26 +10652,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -10682,18 +10678,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr"/>
+          <t>3K</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>-2K</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10708,22 +10708,22 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F414" t="n">
@@ -10738,26 +10738,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>111K</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>141K</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10768,26 +10764,26 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10798,22 +10794,26 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10904,22 +10904,18 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -10934,22 +10930,22 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10964,26 +10960,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="425">
@@ -10994,22 +10986,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11024,18 +11016,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr"/>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11050,22 +11046,26 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428">
@@ -11564,22 +11564,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -11616,18 +11616,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -11638,22 +11642,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F457" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -12574,18 +12574,14 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12600,14 +12596,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12622,22 +12622,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12648,22 +12648,22 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E502" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F502" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="503">
@@ -12674,14 +12674,14 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F503" t="n">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
@@ -13158,14 +13158,14 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr"/>
       <c r="F527" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="528">
@@ -13212,14 +13212,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="531">
@@ -13578,22 +13578,18 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
-      <c r="D549" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D549" t="inlineStr"/>
       <c r="E549" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F549" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="550">
@@ -13648,18 +13644,22 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
@@ -13670,18 +13670,22 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F553" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554">
@@ -13692,22 +13696,18 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="555">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14924,7 +14924,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15210,18 +15210,14 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="D633" t="inlineStr"/>
       <c r="E633" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -15236,11 +15232,15 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
-      <c r="D634" t="inlineStr"/>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E634" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15258,14 +15258,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F635" t="n">
@@ -15462,22 +15462,18 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
-      <c r="D643" t="inlineStr">
-        <is>
-          <t>4.17M</t>
-        </is>
-      </c>
+      <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F643" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="644">
@@ -15614,18 +15610,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
-      <c r="D649" t="inlineStr"/>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="650">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16580,7 +16580,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-26.xlsx
@@ -720,22 +720,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -746,12 +742,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,18 +764,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -790,19 +790,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -816,18 +812,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -838,15 +838,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -860,22 +864,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -886,12 +886,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -974,12 +974,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,22 +1716,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1746,22 +1746,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1776,18 +1772,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,22 +1798,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1832,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1862,18 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2098,14 +2098,26 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+          <t>Total Vehicle SalesDEC</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>16.3M</t>
+        </is>
+      </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -2116,18 +2128,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2142,26 +2158,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2172,26 +2184,14 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>1848K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2202,26 +2202,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2350,18 +2350,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2372,19 +2376,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3</v>
@@ -2424,15 +2424,19 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
         <v>3</v>
@@ -2446,12 +2450,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2468,22 +2472,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2860,22 +2860,18 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2890,22 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,22 +2972,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3006,22 +3002,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3036,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3066,26 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3096,22 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3122,18 +3118,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -3304,14 +3304,10 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3326,10 +3322,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3532,26 +3532,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3562,22 +3562,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3592,22 +3592,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3622,26 +3618,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3652,18 +3644,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3678,22 +3674,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3719,11 +3719,11 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -4010,22 +4010,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -4036,22 +4040,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4070,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4126,26 +4130,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -4156,22 +4160,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4186,26 +4190,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4252,22 +4252,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -4278,22 +4278,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4304,12 +4300,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4326,12 +4322,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4348,12 +4344,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,12 +4366,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,18 +4388,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4414,22 +4414,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -4586,22 +4586,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4616,26 +4616,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4646,22 +4646,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -4672,12 +4676,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -4694,18 +4698,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4720,26 +4724,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4750,24 +4746,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4780,12 +4768,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -4802,18 +4790,26 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -4824,18 +4820,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4850,26 +4846,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4880,26 +4872,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4910,22 +4902,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -4940,26 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4970,12 +4962,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -4992,16 +4984,24 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5014,22 +5014,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5044,26 +5044,26 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5074,17 +5074,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
@@ -5352,18 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5378,26 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -5408,22 +5408,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5438,26 +5438,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -5468,18 +5464,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -5648,12 +5648,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,18 +5942,22 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -5998,22 +6002,18 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6150,22 +6150,18 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
@@ -6176,12 +6172,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,15 +6194,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6220,22 +6220,18 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -6246,12 +6242,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,12 +6264,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,12 +6286,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6312,18 +6308,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6334,19 +6334,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6360,12 +6356,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,18 +6378,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -6534,22 +6534,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6564,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6594,26 +6594,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -6624,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6654,22 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7040,22 +7040,26 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -7066,26 +7070,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -7096,26 +7100,22 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7126,26 +7126,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -7316,26 +7316,22 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
@@ -7346,26 +7342,26 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
@@ -7376,18 +7372,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7402,18 +7402,18 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7704,22 +7704,18 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>$-105.4B</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -7764,18 +7760,22 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
+          <t>$-122.11B</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>$-105.4B</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -8324,18 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8350,22 +8354,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8516,12 +8516,20 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr"/>
+          <t>Employment Cost - Wages QoQQ4</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F326" t="n">
         <v>2</v>
       </c>
@@ -8534,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -8564,22 +8572,18 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8594,26 +8598,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8624,26 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8654,26 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
@@ -8684,18 +8688,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8710,26 +8718,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8740,20 +8748,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="n">
         <v>2</v>
       </c>
@@ -8766,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -8904,22 +8904,18 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -8934,26 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
@@ -8964,26 +8956,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8994,18 +8986,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9020,22 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9206,26 +9206,22 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="354">
@@ -9236,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -9292,18 +9292,18 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F356" t="n">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9590,18 +9590,18 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -9616,26 +9616,14 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -9646,18 +9634,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9672,14 +9660,26 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,26 +9794,22 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -9850,22 +9846,26 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -9902,22 +9902,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -9928,15 +9924,19 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
         <v>3</v>
@@ -9950,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,22 +9972,18 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -9998,12 +9994,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10020,12 +10016,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10042,12 +10038,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,22 +10060,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10090,18 +10086,22 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -10196,22 +10196,26 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr"/>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395">
@@ -10222,22 +10226,22 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F395" t="n">
@@ -10252,26 +10256,26 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397">
@@ -10282,26 +10286,22 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>219K</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="398">
@@ -10312,26 +10312,26 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="399">
@@ -10536,26 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>111K</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>141K</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -10566,18 +10562,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>3K</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>-2K</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10592,22 +10592,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -10618,26 +10622,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -10648,22 +10652,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10678,26 +10682,26 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -10708,18 +10712,22 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F414" t="n">
@@ -10734,22 +10742,18 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F415" t="n">
@@ -10764,26 +10768,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10794,26 +10794,26 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418">
@@ -10904,18 +10904,22 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -10930,22 +10934,22 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,22 +10964,26 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
@@ -10986,22 +10994,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11016,26 +11024,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F426" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="427">
@@ -11046,22 +11050,18 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -11564,22 +11564,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -11616,22 +11616,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -11642,18 +11638,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F457" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="458">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -12574,22 +12574,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -12600,18 +12600,14 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12626,14 +12622,14 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -12648,14 +12644,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12670,22 +12670,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E503" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
@@ -13158,14 +13158,14 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr"/>
       <c r="F527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="528">
@@ -13212,14 +13212,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="531">
@@ -13578,18 +13578,22 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F549" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550">
@@ -13644,22 +13648,18 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -13670,22 +13670,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F553" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -13696,18 +13692,22 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F554" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="555">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14924,7 +14924,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -15210,18 +15210,14 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="D633" t="inlineStr"/>
       <c r="E633" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -15236,11 +15232,15 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
-      <c r="D634" t="inlineStr"/>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E634" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15258,14 +15258,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F635" t="n">
@@ -15462,18 +15462,22 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
-      <c r="D643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F643" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="644">
@@ -15610,22 +15614,18 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
-      <c r="D649" t="inlineStr">
-        <is>
-          <t>4.17M</t>
-        </is>
-      </c>
+      <c r="D649" t="inlineStr"/>
       <c r="E649" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="650">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16580,7 +16580,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
